--- a/stations/output/TVE_Interlocking_Program.xlsx
+++ b/stations/output/TVE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.21.0</t>
+          <t>v0.23.0</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1/3, 5/7, V</t>
+          <t>A1, A2, 1/3, 5/7</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
@@ -1878,14 +1878,10 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1/3, 5/7, V</t>
-        </is>
-      </c>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>6/8, 2/4</t>
-        </is>
-      </c>
+          <t>A1, A2, 1/3, 5/7</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
@@ -2011,11 +2007,7 @@
           <t>A1, A2, 1/3, I</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr">
-        <is>
-          <t>2/4, D1</t>
-        </is>
-      </c>
+      <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
@@ -2141,11 +2133,7 @@
           <t>A1, A2, 1/3, II</t>
         </is>
       </c>
-      <c r="S12" s="12" t="inlineStr">
-        <is>
-          <t>2/4, D1</t>
-        </is>
-      </c>
+      <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
@@ -2275,11 +2263,7 @@
           <t>A1, A2, 1/3, 5/7, III</t>
         </is>
       </c>
-      <c r="S14" s="12" t="inlineStr">
-        <is>
-          <t>6/8, 2/4</t>
-        </is>
-      </c>
+      <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
@@ -2406,7 +2390,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1/3, 5/7, IV</t>
+          <t>A1, A2, 1/3, 5/7</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
@@ -2548,14 +2532,10 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>A1, A2, 1/3, 5/7, IV</t>
-        </is>
-      </c>
-      <c r="S18" s="12" t="inlineStr">
-        <is>
-          <t>6/8, 2/4</t>
-        </is>
-      </c>
+          <t>A1, A2, 1/3, 5/7</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
@@ -2690,7 +2670,7 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8, IV</t>
+          <t>D1, 2/4, 6/8</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
@@ -2832,14 +2812,10 @@
       <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8, IV</t>
-        </is>
-      </c>
-      <c r="S22" s="12" t="inlineStr">
-        <is>
-          <t>5/7, 1/3</t>
-        </is>
-      </c>
+          <t>D1, 2/4, 6/8</t>
+        </is>
+      </c>
+      <c r="S22" s="12" t="inlineStr"/>
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr"/>
       <c r="V22" s="11" t="inlineStr"/>
@@ -2969,11 +2945,7 @@
           <t>D1, 2/4, I</t>
         </is>
       </c>
-      <c r="S24" s="12" t="inlineStr">
-        <is>
-          <t>1/3, A2</t>
-        </is>
-      </c>
+      <c r="S24" s="12" t="inlineStr"/>
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="12" t="inlineStr"/>
       <c r="V24" s="11" t="inlineStr"/>
@@ -3099,11 +3071,7 @@
           <t>D1, 2/4, II</t>
         </is>
       </c>
-      <c r="S26" s="12" t="inlineStr">
-        <is>
-          <t>1/3, A2</t>
-        </is>
-      </c>
+      <c r="S26" s="12" t="inlineStr"/>
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="12" t="inlineStr"/>
       <c r="V26" s="11" t="inlineStr"/>
@@ -3233,11 +3201,7 @@
           <t>D1, 2/4, 6/8, III</t>
         </is>
       </c>
-      <c r="S28" s="12" t="inlineStr">
-        <is>
-          <t>5/7, 1/3</t>
-        </is>
-      </c>
+      <c r="S28" s="12" t="inlineStr"/>
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="12" t="inlineStr"/>
       <c r="V28" s="11" t="inlineStr"/>
@@ -3352,7 +3316,7 @@
       <c r="Q30" s="12" t="inlineStr"/>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8, V, 5/7, 1/3, A2, A1</t>
+          <t>D1, 2/4, 6/8, 5/7, 1/3, A2, A1</t>
         </is>
       </c>
       <c r="S30" s="12" t="inlineStr"/>

--- a/stations/output/TVE_Interlocking_Program.xlsx
+++ b/stations/output/TVE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.23.0</t>
+          <t>v0.24.1</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,11 @@
           <t>A1, A2, 1/3, 5/7</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>6/8, 2/4</t>
+        </is>
+      </c>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
@@ -1998,7 +2002,11 @@
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -2007,11 +2015,19 @@
           <t>A1, A2, 1/3, I</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr"/>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>2/4, D1</t>
+        </is>
+      </c>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
-      <c r="W10" s="12" t="inlineStr"/>
+      <c r="W10" s="12" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="11" t="inlineStr"/>
@@ -2057,7 +2073,11 @@
       <c r="K11" s="12" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -2066,7 +2086,11 @@
       <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
+      <c r="W11" s="12" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
@@ -2124,7 +2148,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -2133,11 +2161,19 @@
           <t>A1, A2, 1/3, II</t>
         </is>
       </c>
-      <c r="S12" s="12" t="inlineStr"/>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>2/4, D1</t>
+        </is>
+      </c>
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="12" t="inlineStr"/>
+      <c r="W12" s="12" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
@@ -2187,7 +2223,11 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -2196,7 +2236,11 @@
       <c r="T13" s="11" t="inlineStr"/>
       <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr"/>
+      <c r="W13" s="12" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -2263,7 +2307,11 @@
           <t>A1, A2, 1/3, 5/7, III</t>
         </is>
       </c>
-      <c r="S14" s="12" t="inlineStr"/>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>6/8, 2/4</t>
+        </is>
+      </c>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
@@ -2535,7 +2583,11 @@
           <t>A1, A2, 1/3, 5/7</t>
         </is>
       </c>
-      <c r="S18" s="12" t="inlineStr"/>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>6/8, 2/4</t>
+        </is>
+      </c>
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
@@ -2815,7 +2867,11 @@
           <t>D1, 2/4, 6/8</t>
         </is>
       </c>
-      <c r="S22" s="12" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr">
+        <is>
+          <t>5/7, 1/3</t>
+        </is>
+      </c>
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr"/>
       <c r="V22" s="11" t="inlineStr"/>
@@ -2938,15 +2994,27 @@
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="12" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q24" s="12" t="inlineStr"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
           <t>D1, 2/4, I</t>
         </is>
       </c>
-      <c r="S24" s="12" t="inlineStr"/>
-      <c r="T24" s="11" t="inlineStr"/>
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>1/3, A2</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U24" s="12" t="inlineStr"/>
       <c r="V24" s="11" t="inlineStr"/>
       <c r="W24" s="12" t="inlineStr"/>
@@ -2997,11 +3065,19 @@
       <c r="M25" s="12" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q25" s="12" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr"/>
       <c r="S25" s="12" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U25" s="12" t="inlineStr"/>
       <c r="V25" s="11" t="inlineStr"/>
       <c r="W25" s="12" t="inlineStr"/>
@@ -3064,15 +3140,27 @@
       </c>
       <c r="N26" s="11" t="inlineStr"/>
       <c r="O26" s="12" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q26" s="12" t="inlineStr"/>
       <c r="R26" s="11" t="inlineStr">
         <is>
           <t>D1, 2/4, II</t>
         </is>
       </c>
-      <c r="S26" s="12" t="inlineStr"/>
-      <c r="T26" s="11" t="inlineStr"/>
+      <c r="S26" s="12" t="inlineStr">
+        <is>
+          <t>1/3, A2</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U26" s="12" t="inlineStr"/>
       <c r="V26" s="11" t="inlineStr"/>
       <c r="W26" s="12" t="inlineStr"/>
@@ -3127,11 +3215,19 @@
       <c r="M27" s="12" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr"/>
       <c r="O27" s="12" t="inlineStr"/>
-      <c r="P27" s="11" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q27" s="12" t="inlineStr"/>
       <c r="R27" s="11" t="inlineStr"/>
       <c r="S27" s="12" t="inlineStr"/>
-      <c r="T27" s="11" t="inlineStr"/>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U27" s="12" t="inlineStr"/>
       <c r="V27" s="11" t="inlineStr"/>
       <c r="W27" s="12" t="inlineStr"/>
@@ -3201,7 +3297,11 @@
           <t>D1, 2/4, 6/8, III</t>
         </is>
       </c>
-      <c r="S28" s="12" t="inlineStr"/>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>5/7, 1/3</t>
+        </is>
+      </c>
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="12" t="inlineStr"/>
       <c r="V28" s="11" t="inlineStr"/>
@@ -6066,7 +6166,11 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -6129,7 +6233,11 @@
       <c r="K9" s="12" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -6192,7 +6300,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -6259,7 +6371,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -6580,7 +6696,11 @@
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -6639,7 +6759,11 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U17" s="12" t="inlineStr"/>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
@@ -6706,7 +6830,11 @@
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
@@ -6769,7 +6897,11 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -16395,7 +16527,11 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
@@ -16454,7 +16590,11 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -16680,7 +16820,11 @@
       <c r="K12" s="12" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -16739,7 +16883,11 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -20002,7 +20150,11 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -20061,7 +20213,11 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -20449,7 +20605,11 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -20508,7 +20668,11 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -24262,191 +24426,191 @@
       </c>
       <c r="C17" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OL_delay_dist_weight 0.18
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI 1
+</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5 63762 63814
+</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OL_delay_dist_bias 15
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI 3
+</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    7 63812 63854
+</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARC_delay_dist_weight 0.08
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE D A2
+</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2 64335 64280
+</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SIG M1
+</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4 64299 64252
+</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC 5/7
+</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    6 64255 64205
+</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_min_delay 60
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE A III
+</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    8 64220 64173
+</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_max_delay 255
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWP S8/M8
+</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    C1 63861
+</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_multiple 5
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE B IV
+</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    C3 63861
+</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_down_allowed False
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWP S10/M10
+</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    C2 64166
+</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">shunt_sig_filters_fp True
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI 1
-</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    5 63762 63814
-</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_weight 0.18
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI 3
-</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    7 63812 63854
-</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_bias 15
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE D A2
-</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2 64335 64280
-</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARC_delay_dist_weight 0.08
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SIG M1
-</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    4 64299 64252
-</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEC 5/7
-</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    6 64255 64205
-</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE A III
-</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    8 64220 64173
-</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_min_delay 60
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWP S8/M8
-</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    C1 63861
-</t>
-        </is>
-      </c>
-      <c r="C24" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_max_delay 255
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE B IV
-</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    C3 63861
-</t>
-        </is>
-      </c>
-      <c r="C25" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_multiple 5
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWP S10/M10
-</t>
-        </is>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    C2 64166
-</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_down_allowed False
-</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
@@ -24460,7 +24624,12 @@
 </t>
         </is>
       </c>
-      <c r="C27" s="41" t="n"/>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vital_fp_threshold 6
+</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
@@ -24475,7 +24644,12 @@
 </t>
         </is>
       </c>
-      <c r="C28" s="41" t="n"/>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sub_vital_fp_threshold 50
+</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
@@ -24490,7 +24664,12 @@
 </t>
         </is>
       </c>
-      <c r="C29" s="41" t="n"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remote_fp_threshold 150
+</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="inlineStr">

--- a/stations/output/TVE_Interlocking_Program.xlsx
+++ b/stations/output/TVE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.1</t>
+          <t>v1.0.0</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,11 @@
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1787,12 +1791,12 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>C4+</t>
+          <t>C4-</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr"/>
@@ -1803,18 +1807,34 @@
           <t>1, 3, 5, 7, C3</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>6, 8, C4, 4</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
-      <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="12" t="inlineStr"/>
+      <c r="R7" s="11" t="inlineStr">
+        <is>
+          <t>A1, A2, 1/3, 5/7</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>6/8, 2/4</t>
+        </is>
+      </c>
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
@@ -1850,12 +1870,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>C4-</t>
+          <t>C4+</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr"/>
@@ -1866,26 +1886,22 @@
           <t>1, 3, 5, 7, C3</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>6, 8, C4, 4</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>A1, A2, 1/3, 5/7</t>
-        </is>
-      </c>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>6/8, 2/4</t>
-        </is>
-      </c>
+      <c r="R8" s="11" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
@@ -1943,9 +1959,17 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
@@ -2020,7 +2044,11 @@
           <t>2/4, D1</t>
         </is>
       </c>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr">
@@ -2083,7 +2111,11 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr">
@@ -2166,7 +2198,11 @@
           <t>2/4, D1</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr">
@@ -2233,7 +2269,11 @@
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr">
@@ -2298,9 +2338,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
@@ -2365,9 +2413,17 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
@@ -2432,7 +2488,11 @@
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -2477,12 +2537,12 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>C2+</t>
+          <t>C2-</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr"/>
@@ -2499,16 +2559,36 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>6, C2, 4</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="Q17" s="12" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
-      <c r="S17" s="12" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr">
+        <is>
+          <t>A1, A2, 1/3, 5/7</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>6/8, 2/4</t>
+        </is>
+      </c>
       <c r="T17" s="11" t="inlineStr"/>
       <c r="U17" s="12" t="inlineStr"/>
       <c r="V17" s="11" t="inlineStr"/>
@@ -2544,12 +2624,12 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>C2-</t>
+          <t>C2+</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr"/>
@@ -2566,28 +2646,20 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>6, C2, 4</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr">
-        <is>
-          <t>A1, A2, 1/3, 5/7</t>
-        </is>
-      </c>
-      <c r="S18" s="12" t="inlineStr">
-        <is>
-          <t>6/8, 2/4</t>
-        </is>
-      </c>
+      <c r="R18" s="11" t="inlineStr"/>
+      <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
@@ -2649,9 +2721,17 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
@@ -2716,7 +2796,11 @@
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -2761,12 +2845,12 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>C1+</t>
+          <t>C1-</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr"/>
@@ -2783,16 +2867,36 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>5, C1</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O21" s="12" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="Q21" s="12" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="12" t="inlineStr"/>
+      <c r="R21" s="11" t="inlineStr">
+        <is>
+          <t>D1, 2/4, 6/8</t>
+        </is>
+      </c>
+      <c r="S21" s="12" t="inlineStr">
+        <is>
+          <t>5/7, 1/3</t>
+        </is>
+      </c>
       <c r="T21" s="11" t="inlineStr"/>
       <c r="U21" s="12" t="inlineStr"/>
       <c r="V21" s="11" t="inlineStr"/>
@@ -2828,12 +2932,12 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>C1-</t>
+          <t>C1+</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr"/>
@@ -2850,28 +2954,20 @@
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M22" s="12" t="inlineStr">
-        <is>
-          <t>5, C1</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="11" t="inlineStr"/>
       <c r="Q22" s="12" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr">
-        <is>
-          <t>D1, 2/4, 6/8</t>
-        </is>
-      </c>
-      <c r="S22" s="12" t="inlineStr">
-        <is>
-          <t>5/7, 1/3</t>
-        </is>
-      </c>
+      <c r="R22" s="11" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr"/>
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr"/>
       <c r="V22" s="11" t="inlineStr"/>
@@ -2933,9 +3029,17 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O23" s="12" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="Q23" s="12" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr"/>
       <c r="S23" s="12" t="inlineStr"/>
@@ -3017,7 +3121,11 @@
       </c>
       <c r="U24" s="12" t="inlineStr"/>
       <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="12" t="inlineStr"/>
+      <c r="W24" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="X24" s="11" t="inlineStr"/>
       <c r="Y24" s="12" t="inlineStr"/>
       <c r="Z24" s="11" t="inlineStr"/>
@@ -3080,7 +3188,11 @@
       </c>
       <c r="U25" s="12" t="inlineStr"/>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="12" t="inlineStr"/>
+      <c r="W25" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="X25" s="11" t="inlineStr"/>
       <c r="Y25" s="12" t="inlineStr"/>
       <c r="Z25" s="11" t="inlineStr"/>
@@ -3163,7 +3275,11 @@
       </c>
       <c r="U26" s="12" t="inlineStr"/>
       <c r="V26" s="11" t="inlineStr"/>
-      <c r="W26" s="12" t="inlineStr"/>
+      <c r="W26" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="X26" s="11" t="inlineStr"/>
       <c r="Y26" s="12" t="inlineStr"/>
       <c r="Z26" s="11" t="inlineStr"/>
@@ -3230,7 +3346,11 @@
       </c>
       <c r="U27" s="12" t="inlineStr"/>
       <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="12" t="inlineStr"/>
+      <c r="W27" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="X27" s="11" t="inlineStr"/>
       <c r="Y27" s="12" t="inlineStr"/>
       <c r="Z27" s="11" t="inlineStr"/>
@@ -3288,9 +3408,17 @@
           <t>1, 3</t>
         </is>
       </c>
-      <c r="N28" s="11" t="inlineStr"/>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="O28" s="12" t="inlineStr"/>
-      <c r="P28" s="11" t="inlineStr"/>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="Q28" s="12" t="inlineStr"/>
       <c r="R28" s="11" t="inlineStr">
         <is>
@@ -3355,9 +3483,17 @@
       </c>
       <c r="L29" s="11" t="inlineStr"/>
       <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="11" t="inlineStr"/>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="O29" s="12" t="inlineStr"/>
-      <c r="P29" s="11" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="Q29" s="12" t="inlineStr"/>
       <c r="R29" s="11" t="inlineStr"/>
       <c r="S29" s="12" t="inlineStr"/>
@@ -3410,7 +3546,11 @@
       </c>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="11" t="inlineStr"/>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>C2, C1</t>
+        </is>
+      </c>
       <c r="O30" s="12" t="inlineStr"/>
       <c r="P30" s="11" t="inlineStr"/>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -3473,7 +3613,11 @@
       </c>
       <c r="L31" s="11" t="inlineStr"/>
       <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="11" t="inlineStr"/>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>C2, C1</t>
+        </is>
+      </c>
       <c r="O31" s="12" t="inlineStr"/>
       <c r="P31" s="11" t="inlineStr"/>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -6040,7 +6184,11 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -6107,7 +6255,11 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -6180,7 +6332,11 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -6243,7 +6399,11 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -6314,7 +6474,11 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
@@ -6381,7 +6545,11 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
@@ -6438,7 +6606,11 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -6505,7 +6677,11 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -6564,7 +6740,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -6627,7 +6807,11 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -6958,7 +7142,11 @@
       </c>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -7025,7 +7213,11 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="O21" s="12" t="inlineStr"/>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -7088,7 +7280,11 @@
       </c>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="11" t="inlineStr"/>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -7155,7 +7351,11 @@
       </c>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O23" s="12" t="inlineStr"/>
       <c r="P23" s="11" t="inlineStr"/>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -16466,7 +16666,11 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -16647,7 +16851,11 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -16706,7 +16914,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -16765,7 +16977,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -16830,7 +17046,11 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
@@ -16893,7 +17113,11 @@
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
@@ -16946,7 +17170,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -17001,7 +17229,11 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -20032,7 +20264,11 @@
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -20095,9 +20331,17 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
@@ -20160,7 +20404,11 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -20223,7 +20471,11 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -20276,7 +20528,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>C1, C3</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -20343,7 +20599,11 @@
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -20410,9 +20670,17 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
@@ -20477,7 +20745,11 @@
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -20544,9 +20816,17 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
@@ -20725,7 +21005,11 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>C4, C2</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -20788,7 +21072,11 @@
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -20851,9 +21139,17 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>

--- a/stations/output/TVE_Interlocking_Program.xlsx
+++ b/stations/output/TVE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.1</t>
         </is>
       </c>
     </row>

--- a/stations/output/TVE_Interlocking_Program.xlsx
+++ b/stations/output/TVE_Interlocking_Program.xlsx
@@ -24358,7 +24358,7 @@
       </c>
       <c r="C1" s="36" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Operational Parameters</t>
         </is>
       </c>
       <c r="D1" s="37" t="inlineStr">

--- a/stations/output/TVE_Interlocking_Program.xlsx
+++ b/stations/output/TVE_Interlocking_Program.xlsx
@@ -462,15 +462,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -479,37 +470,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,30 +491,6 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
@@ -585,6 +521,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -592,6 +561,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -609,6 +587,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -639,12 +628,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -788,9 +788,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,29 +815,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1183,49 +1193,49 @@
       <c r="B1" s="21" t="n"/>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="21" t="n"/>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>ZIRCON</t>
         </is>
       </c>
-      <c r="F1" s="60" t="n"/>
+      <c r="F1" s="62" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="61" t="n"/>
-      <c r="F2" s="62" t="n"/>
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
+      <c r="A3" s="58" t="n"/>
+      <c r="B3" s="59" t="n"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="59" t="n"/>
+      <c r="E3" s="59" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.1</t>
+          <t>v1.0.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="49" t="n"/>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="58" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
+      <c r="A5" s="58" t="n"/>
       <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Interlocking Program</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="60" t="n"/>
     </row>
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="24" t="n"/>
@@ -1240,94 +1250,92 @@
       <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Torres Vedras (TVE)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>Torres Vedras (NOT REAL DATA - FOR TESTING ONLY) (TVE)</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Linha do Oeste</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
@@ -1335,11 +1343,11 @@
           <t>Diogo Luís</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1355,9 +1363,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1385,310 +1393,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -2041,7 +2049,7 @@
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>2/4, D1</t>
+          <t>2/4, B1</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr">
@@ -2195,7 +2203,7 @@
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>2/4, D1</t>
+          <t>2/4, B1</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr">
@@ -2750,7 +2758,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2806,7 +2814,7 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8</t>
+          <t>B1, 2/4, 6/8</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
@@ -2825,7 +2833,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2889,7 +2897,7 @@
       <c r="Q21" s="12" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8</t>
+          <t>B1, 2/4, 6/8</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
@@ -2912,7 +2920,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2983,7 +2991,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -3058,7 +3066,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -3106,7 +3114,7 @@
       <c r="Q24" s="12" t="inlineStr"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, I</t>
+          <t>B1, 2/4, I</t>
         </is>
       </c>
       <c r="S24" s="12" t="inlineStr">
@@ -3137,7 +3145,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3204,7 +3212,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -3260,7 +3268,7 @@
       <c r="Q26" s="12" t="inlineStr"/>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, II</t>
+          <t>B1, 2/4, II</t>
         </is>
       </c>
       <c r="S26" s="12" t="inlineStr">
@@ -3291,7 +3299,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -3362,7 +3370,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -3422,7 +3430,7 @@
       <c r="Q28" s="12" t="inlineStr"/>
       <c r="R28" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8, III</t>
+          <t>B1, 2/4, 6/8, III</t>
         </is>
       </c>
       <c r="S28" s="12" t="inlineStr">
@@ -3445,7 +3453,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3512,7 +3520,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3556,7 +3564,7 @@
       <c r="Q30" s="12" t="inlineStr"/>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>D1, 2/4, 6/8, 5/7, 1/3, A2, A1</t>
+          <t>B1, 2/4, 6/8, 5/7, 1/3, A2, A1</t>
         </is>
       </c>
       <c r="S30" s="12" t="inlineStr"/>
@@ -3579,7 +3587,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -5831,310 +5839,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -6750,7 +6758,7 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>6/8, 2/4, D1</t>
+          <t>6/8, 2/4, B1</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
@@ -6876,7 +6884,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>2/4, D1</t>
+          <t>2/4, B1</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
@@ -7010,7 +7018,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>2/4, D1</t>
+          <t>2/4, B1</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
@@ -7152,7 +7160,7 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>6/8, 2/4, D1</t>
+          <t>6/8, 2/4, B1</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
@@ -7290,7 +7298,7 @@
       <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>6/8, 2/4, D1</t>
+          <t>6/8, 2/4, B1</t>
         </is>
       </c>
       <c r="S22" s="12" t="inlineStr"/>
@@ -9801,310 +9809,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -13059,310 +13067,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -16317,310 +16325,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -16647,7 +16655,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -16706,7 +16714,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -16765,7 +16773,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -16828,7 +16836,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -16891,7 +16899,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -19907,310 +19915,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -20704,7 +20712,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -20775,7 +20783,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -20850,7 +20858,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -20909,7 +20917,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -20972,7 +20980,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -21035,7 +21043,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -21102,7 +21110,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -23698,24 +23706,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="B1" s="66" t="n"/>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="B1" s="70" t="n"/>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Approach Route Cancel</t>
         </is>
       </c>
-      <c r="D1" s="66" t="n"/>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="D1" s="70" t="n"/>
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Emergency Route Cancel</t>
         </is>
       </c>
-      <c r="F1" s="66" t="n"/>
+      <c r="F1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -23723,27 +23731,27 @@
           <t>Track</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
@@ -23950,7 +23958,7 @@
       <c r="B11" s="12" t="n"/>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
@@ -24000,7 +24008,7 @@
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
@@ -24388,7 +24396,7 @@
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">station_name Torres Vedras
+          <t xml:space="preserve">station_name Torres Vedras (NOT REAL DATA - FOR TESTING ONLY)
 </t>
         </is>
       </c>
@@ -24402,7 +24410,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A1 63441 63230
+          <t xml:space="preserve">    A1 93441 93230
 </t>
         </is>
       </c>
@@ -24428,7 +24436,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A2 63658 63441
+          <t xml:space="preserve">    A2 93658 93441
 </t>
         </is>
       </c>
@@ -24454,7 +24462,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1/3 63750 63784 63740 63658
+          <t xml:space="preserve">    1/3 93750 93784 93740 93658
 </t>
         </is>
       </c>
@@ -24480,7 +24488,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5/7 63820 63860 63860 63740
+          <t xml:space="preserve">    5/7 93820 93860 93860 93740
 </t>
         </is>
       </c>
@@ -24506,7 +24514,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    I 64265 63750
+          <t xml:space="preserve">    I 94265 93750
 </t>
         </is>
       </c>
@@ -24527,7 +24535,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    II 64227 63784
+          <t xml:space="preserve">    II 94227 93784
 </t>
         </is>
       </c>
@@ -24548,7 +24556,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    III 64170 63820
+          <t xml:space="preserve">    III 94170 93820
 </t>
         </is>
       </c>
@@ -24569,7 +24577,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IV 64167 63860
+          <t xml:space="preserve">    IV 94167 93860
 </t>
         </is>
       </c>
@@ -24590,7 +24598,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    V 64167 63860
+          <t xml:space="preserve">    V 94167 93860
 </t>
         </is>
       </c>
@@ -24611,7 +24619,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2/4 64355 64275 64227 64265
+          <t xml:space="preserve">    2/4 94355 94275 94227 94265
 </t>
         </is>
       </c>
@@ -24632,7 +24640,7 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6/8 64275 64167 64167 64170
+          <t xml:space="preserve">    6/8 94275 94167 94167 94170
 </t>
         </is>
       </c>
@@ -24653,7 +24661,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D1 64800 64355
+          <t xml:space="preserve">    B1 94800 94355
 </t>
         </is>
       </c>
@@ -24695,7 +24703,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1 63678 63734
+          <t xml:space="preserve">    1 93678 93734
 </t>
         </is>
       </c>
@@ -24716,7 +24724,7 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 63715 63765
+          <t xml:space="preserve">    3 93715 93765
 </t>
         </is>
       </c>
@@ -24736,7 +24744,7 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 63762 63814
+          <t xml:space="preserve">    5 93762 93814
 </t>
         </is>
       </c>
@@ -24756,7 +24764,7 @@
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7 63812 63854
+          <t xml:space="preserve">    7 93812 93854
 </t>
         </is>
       </c>
@@ -24776,7 +24784,7 @@
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 64335 64280
+          <t xml:space="preserve">    2 94335 94280
 </t>
         </is>
       </c>
@@ -24796,7 +24804,7 @@
       </c>
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4 64299 64252
+          <t xml:space="preserve">    4 94299 94252
 </t>
         </is>
       </c>
@@ -24816,7 +24824,7 @@
       </c>
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6 64255 64205
+          <t xml:space="preserve">    6 94255 94205
 </t>
         </is>
       </c>
@@ -24836,7 +24844,7 @@
       </c>
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8 64220 64173
+          <t xml:space="preserve">    8 94220 94173
 </t>
         </is>
       </c>
@@ -24856,7 +24864,7 @@
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C1 63861
+          <t xml:space="preserve">    C1 93861
 </t>
         </is>
       </c>
@@ -24876,7 +24884,7 @@
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C3 63861
+          <t xml:space="preserve">    C3 93861
 </t>
         </is>
       </c>
@@ -24896,7 +24904,7 @@
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C2 64166
+          <t xml:space="preserve">    C2 94166
 </t>
         </is>
       </c>
@@ -24916,7 +24924,7 @@
       </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    C4 64166
+          <t xml:space="preserve">    C4 94166
 </t>
         </is>
       </c>
@@ -24956,7 +24964,7 @@
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 63222 60200 350
+          <t xml:space="preserve">    S1 93222 90200 350
 </t>
         </is>
       </c>
@@ -24976,7 +24984,7 @@
       </c>
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_A1 63441
+          <t xml:space="preserve">    M_A1 93441
 </t>
         </is>
       </c>
@@ -24991,7 +24999,7 @@
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M1 63658
+          <t xml:space="preserve">    M1 93658
 </t>
         </is>
       </c>
@@ -25006,7 +25014,7 @@
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4/M4 63755 66285 350
+          <t xml:space="preserve">    S4/M4 93755 96285 350
 </t>
         </is>
       </c>
@@ -25020,7 +25028,7 @@
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6/M6 63789 66285 350
+          <t xml:space="preserve">    S6/M6 93789 96285 350
 </t>
         </is>
       </c>
@@ -25034,7 +25042,7 @@
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S8/M8 63825 66285 350
+          <t xml:space="preserve">    S8/M8 93825 96285 350
 </t>
         </is>
       </c>
@@ -25048,7 +25056,7 @@
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M12 63863
+          <t xml:space="preserve">    M12 93863
 </t>
         </is>
       </c>
@@ -25062,7 +25070,7 @@
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S10/M10 63868 66285 350
+          <t xml:space="preserve">    S10/M10 93868 96285 350
 </t>
         </is>
       </c>
@@ -25076,7 +25084,7 @@
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S11/M11 64159
+          <t xml:space="preserve">    S11/M11 94159
 </t>
         </is>
       </c>
@@ -25090,7 +25098,7 @@
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S9/M9 64159
+          <t xml:space="preserve">    S9/M9 94159
 </t>
         </is>
       </c>
@@ -25104,7 +25112,7 @@
       </c>
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S7/M7 64165 61580 350
+          <t xml:space="preserve">    S7/M7 94165 91580 350
 </t>
         </is>
       </c>
@@ -25118,7 +25126,7 @@
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S5/M5 64222 61580 350
+          <t xml:space="preserve">    S5/M5 94222 91580 350
 </t>
         </is>
       </c>
@@ -25132,7 +25140,7 @@
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S3/M3 64250 61580 350
+          <t xml:space="preserve">    S3/M3 94250 91580 350
 </t>
         </is>
       </c>
@@ -25146,7 +25154,7 @@
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M2 64356
+          <t xml:space="preserve">    M2 94356
 </t>
         </is>
       </c>
@@ -25160,7 +25168,7 @@
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2 64807 66285 350
+          <t xml:space="preserve">    S20 94807 96285 350
 </t>
         </is>
       </c>
@@ -25174,7 +25182,7 @@
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_RAM 64775
+          <t xml:space="preserve">    M_RAM 94775
 </t>
         </is>
       </c>
@@ -25236,7 +25244,7 @@
     <row r="51">
       <c r="A51" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A D1
+          <t xml:space="preserve">    NDE A B1
 </t>
         </is>
       </c>
@@ -25443,7 +25451,7 @@
     <row r="74">
       <c r="A74" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D1
+          <t xml:space="preserve">SEC B1
 </t>
         </is>
       </c>
@@ -25461,7 +25469,7 @@
     <row r="76">
       <c r="A76" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWP S2
+          <t xml:space="preserve">        SWP S20
 </t>
         </is>
       </c>
